--- a/excel/output_stats_sfvv/3mm/EfficiencyStats.xlsx
+++ b/excel/output_stats_sfvv/3mm/EfficiencyStats.xlsx
@@ -490,28 +490,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42.458</v>
+        <v>42.5422</v>
       </c>
       <c r="D2" t="n">
-        <v>0.018281</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>42.4914</v>
+        <v>42.5422</v>
       </c>
       <c r="F2" t="n">
         <v>356.66</v>
       </c>
       <c r="G2" t="n">
-        <v>357.18</v>
+        <v>359.84</v>
       </c>
       <c r="H2" t="n">
-        <v>343.181</v>
+        <v>339.448</v>
       </c>
       <c r="I2" t="n">
-        <v>343.183</v>
+        <v>339.464</v>
       </c>
       <c r="J2" t="n">
-        <v>31107500000</v>
+        <v>31125600000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
